--- a/data/gravel/Breezer Radar X 2025.xlsx
+++ b/data/gravel/Breezer Radar X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E591B8FD-BD72-6847-B048-E54D4DECDFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49107A-0108-3C4E-AE34-9533C3902E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6700" yWindow="3640" windowWidth="22100" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>seat_post_diameter_mm</t>
+  </si>
+  <si>
+    <t>https://www.breezerbikes.com/cdn/shop/files/2021_BREEZER_RADAR_X_PRO_DEEPPURPLE.jpg?v=1744049929&amp;width=1400</t>
   </si>
 </sst>
 </file>
@@ -729,6 +732,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Breezer Radar X 2025.xlsx
+++ b/data/gravel/Breezer Radar X 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49107A-0108-3C4E-AE34-9533C3902E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2A2C27-1477-394C-96C1-C4406C50A757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6700" yWindow="3640" windowWidth="22100" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t>https://www.breezerbikes.com/cdn/shop/files/2021_BREEZER_RADAR_X_PRO_DEEPPURPLE.jpg?v=1744049929&amp;width=1400</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania, USA</t>
   </si>
 </sst>
 </file>
@@ -686,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1617,6 +1623,14 @@
         <v>105</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Breezer Radar X 2025.xlsx
+++ b/data/gravel/Breezer Radar X 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2A2C27-1477-394C-96C1-C4406C50A757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F98AE0-B38C-8640-B8F4-D4E70CA63C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6700" yWindow="3640" windowWidth="22100" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21400" yWindow="-19680" windowWidth="22100" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1333,22 +1333,22 @@
         <v>56</v>
       </c>
       <c r="C31">
+        <v>157.5</v>
+      </c>
+      <c r="D31">
         <v>165</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>173</v>
       </c>
-      <c r="E31">
-        <v>179</v>
-      </c>
       <c r="F31">
+        <v>178</v>
+      </c>
+      <c r="G31">
         <v>183</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>188</v>
-      </c>
-      <c r="H31">
-        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1356,19 +1356,19 @@
         <v>57</v>
       </c>
       <c r="C32">
+        <v>165</v>
+      </c>
+      <c r="D32">
         <v>173</v>
       </c>
-      <c r="D32">
-        <v>179</v>
-      </c>
       <c r="E32">
+        <v>180.5</v>
+      </c>
+      <c r="F32">
         <v>183</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>188</v>
-      </c>
-      <c r="G32">
-        <v>193</v>
       </c>
       <c r="H32">
         <v>195.5</v>

--- a/data/gravel/Breezer Radar X 2025.xlsx
+++ b/data/gravel/Breezer Radar X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F98AE0-B38C-8640-B8F4-D4E70CA63C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1537A6B2-0AFA-1D42-B07D-16BCF7737A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21400" yWindow="-19680" windowWidth="22100" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -353,6 +353,24 @@
   </si>
   <si>
     <t>Philadelphia, Pennsylvania, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -692,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1475,159 +1493,189 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51">
-        <v>30.9</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B57">
+        <v>30.9</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>86</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>88</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>90</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>93</v>
-      </c>
-      <c r="B70">
-        <v>1699</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>109</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>110</v>
       </c>
     </row>
